--- a/docs/测试渠道热销数据.xlsx
+++ b/docs/测试渠道热销数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="渠道热销数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="渠道热销" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,9 +26,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -40,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ea0345"/>
+        <fgColor rgb="00000947"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,11 +90,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +467,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -493,7 +498,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Agoda</t>
@@ -501,7 +506,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HSNEW00001</t>
+          <t>HID10001</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -516,11 +521,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>港区六本木 101 号</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>港区六本木 Hill 101 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>AgodaUK</t>
@@ -528,7 +533,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>HSNEW00002</t>
+          <t>HID10002</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -543,11 +548,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Mayfair Oxford St 55</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Mayfair Oxford Street 55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AgodaEBK</t>
@@ -555,7 +560,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HSNEW00003</t>
+          <t>HID10003</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -570,11 +575,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Champs-Élysées 88</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Champs-Élysées Avenue 88</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Lvzan</t>
@@ -582,7 +587,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>HSNEW00004</t>
+          <t>HID10004</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -592,16 +597,16 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>清迈</t>
+          <t>曼谷</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Nimmanhaemin Rd 22 Chiang Mai</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>Sukhumvit Road Soi 11 Bangkok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Barli2b</t>
@@ -609,7 +614,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HSNEW00005</t>
+          <t>HID10005</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -624,11 +629,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Marina Bay Sands Blvd 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>Orchard Road #03-22 Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>DidaOpaq</t>
@@ -636,400 +641,400 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HSNEW00006</t>
+          <t>HID10006</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>中区明洞 2 街 30 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HID10007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>悉尼</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100 George Street Sydney NSW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AgodaUK</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>HID10008</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>阿联酋</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>迪拜</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Palm Jumeirah Island 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed Road Tower C Dubai</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AgodaEBK</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>HID10009</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>吉隆坡</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Jalan Bukit Bintang 12 KL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Lvzan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>HID10010</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>巴厘岛</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Legian Street No.66 Kuta Bali</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Barli2b</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HID10011</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>胡志明市</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Dong Khoi Street 45 District 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DidaOpaq</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>HID10012</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>朝阳区建国路 SOHO 现代城 8 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Agoda</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00007</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>HID10013</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>浦东新区陆家嘴环路 1088 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AgodaUK</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>HID10014</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>中央区道顿堀 2 番地 Namba Walk</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AgodaEBK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>HID10015</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>普吉</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Patong Beach Road 23 Kathu Phuket</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Lvzan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>HID10016</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>韩国</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>首尔</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>江南区清潭洞 77 号</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>釜山</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>海云台区海水욕场路 18 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Barli2b</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>HID10017</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>河内</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Hoan Kiem Street 7 Hanoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DidaOpaq</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>HID10018</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>锦江区春熙路太古里 5 号</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>HID10019</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Marina Bay Sands Avenue 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>AgodaUK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00008</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>HID10020</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>澳大利亚</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>墨尔本</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Collins Street 200 Melbourne</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>AgodaEBK</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00009</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>马来西亚</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>槟城</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Georgetown Heritage Trail 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Lvzan</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00010</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>印度尼西亚</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>雅加达</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Jl. MH Thamrin 28 Jakarta</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Barli2b</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00011</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>岘港</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Vo Nguyen Giap St 60 Da Nang</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>DidaOpaq</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00012</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>三亚</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>亚龙湾景区路 88 号</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Agoda</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00013</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>冲绳</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Kokusai-dori 14 Naha</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>AgodaUK</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00014</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>泰国</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>苏梅岛</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Chaweng Beach Rd 33 Koh Samui</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>AgodaEBK</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00015</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>孟买</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Marine Drive 10 Mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Lvzan</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00016</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>西安</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>雁塔区大雁塔北广场 6 号</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Barli2b</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00017</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>菲律宾</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>宿务</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Mactan Island Resort Rd 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>DidaOpaq</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00018</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>丽江</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>古城区四方街 15 号</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agoda</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>HSNEW00019</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>斯里兰卡</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>科伦坡</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Galle Road 120 Colombo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>AgodaUK</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>HSNEW00020</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>马尔代夫</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>马累</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>North Malé Atoll Resort</t>
+          <t>200 Collins Street Melbourne VIC</t>
         </is>
       </c>
     </row>
